--- a/Exam/gymtrackerpro/lib/controller/__tests__/it/exercise-controller/updateExercise-it-form.xlsx
+++ b/Exam/gymtrackerpro/lib/controller/__tests__/it/exercise-controller/updateExercise-it-form.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="69">
   <si>
     <t>Statement: updateExercise(id: string, data: UpdateExerciseInput): Promise&lt;ActionResult&lt;Exercise&gt;&gt; - validates input with Zod, delegates to exerciseService.updateExercise(), and returns the updated entity wrapped in ActionResult.</t>
   </si>
@@ -101,6 +101,22 @@
     <t>2</t>
   </si>
   <si>
+    <t xml:space="preserve">Exercise "Squat" (LEGS, BARBELL, description: "Original description") seeded via exerciseService.create().
+const data: UpdateExerciseInput = { name: "Barbell Back Squat" }</t>
+  </si>
+  <si>
+    <t>{ success: true, data: { name: "Barbell Back Squat" } }</t>
+  </si>
+  <si>
+    <t>Row name updated; description = "Original description", muscleGroup = LEGS, equipmentNeeded = BARBELL all unchanged</t>
+  </si>
+  <si>
+    <t>Not yet run</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t xml:space="preserve">Exercise "Bench Press" (CHEST) seeded via exerciseService.create().
 const data: UpdateExerciseInput = { name: "Bench Press", description: "New description" }</t>
   </si>
@@ -111,7 +127,7 @@
     <t>description updated; name unchanged (self-reference permitted)</t>
   </si>
   <si>
-    <t>3</t>
+    <t>4</t>
   </si>
   <si>
     <t xml:space="preserve">Empty database.
@@ -128,7 +144,7 @@
     <t>No change</t>
   </si>
   <si>
-    <t>4</t>
+    <t>5</t>
   </si>
   <si>
     <t xml:space="preserve">"Bench Press" seeded via exerciseService.create(). "Squat" seeded via exerciseService.create().
@@ -144,7 +160,7 @@
     <t>Squat row name unchanged in exercises table</t>
   </si>
   <si>
-    <t>5</t>
+    <t>6</t>
   </si>
   <si>
     <t xml:space="preserve">Empty database.
@@ -157,14 +173,14 @@
     <t>{ success: false, message: "Validation failed", errors: { name: [...] } }</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exercise "Squat" (LEGS, BARBELL, description: "Original") seeded via exerciseService.create().
+    <t>7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exercise "Squat" (LEGS, BARBELL, description: "Original description") seeded via exerciseService.create().
 const data: UpdateExerciseInput = {}</t>
   </si>
   <si>
-    <t>{ success: true, data: all fields identical to the seeded row }</t>
+    <t>{ success: true, data: { name: "Squat", description: "Original description", muscleGroup: LEGS, equipmentNeeded: BARBELL } }</t>
   </si>
   <si>
     <t>All fields in the exercises row unchanged</t>
@@ -219,7 +235,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -237,8 +253,11 @@
     <font>
       <color rgb="FF375623"/>
     </font>
+    <font>
+      <color rgb="FF9C0006"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -265,6 +284,11 @@
         <fgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -285,7 +309,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -303,6 +327,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -852,7 +879,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
@@ -927,8 +954,8 @@
       <c r="F3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>26</v>
+      <c r="G3" s="7" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="4" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -936,13 +963,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>34</v>
@@ -977,7 +1004,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -994,7 +1021,7 @@
         <v>44</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>26</v>
@@ -1005,21 +1032,44 @@
         <v>1</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G7" s="6" t="s">
+      <c r="E8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="6" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1041,24 +1091,24 @@
     <row r="2" spans="1:13" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25"/>
     <row r="4" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="7" t="s">
+      <c r="A4" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -1070,40 +1120,40 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="H5" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="K5" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="J5" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>54</v>
-      </c>
       <c r="L5" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1111,40 +1161,40 @@
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C6" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
